--- a/data/trans_orig/P5_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>28911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33246</t>
+          <t>33239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>69960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84154</t>
+          <t>83463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22723</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>25802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28286</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>44682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>44765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56318</t>
+          <t>55821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38947</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87896</t>
+          <t>88138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104534</t>
+          <t>104017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27731</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>53159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36966</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49021</t>
+          <t>48936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79685</t>
+          <t>79441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96901</t>
+          <t>97201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41612</t>
+          <t>41830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43715</t>
+          <t>43314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55022</t>
+          <t>55224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>49864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61648</t>
+          <t>62015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97957</t>
+          <t>97739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114007</t>
+          <t>114196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34948</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42657</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41137</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49030</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78341</t>
+          <t>77915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89804</t>
+          <t>90062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23630</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38848</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49139</t>
+          <t>49458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70718</t>
+          <t>71357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71798</t>
+          <t>71937</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87016</t>
+          <t>87447</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72077</t>
+          <t>73986</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88164</t>
+          <t>88743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>150715</t>
+          <t>150076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>172294</t>
+          <t>171975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>40394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44150</t>
+          <t>44155</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59297</t>
+          <t>59492</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80460</t>
+          <t>79914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>49773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>64696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52427</t>
+          <t>52422</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66888</t>
+          <t>67293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106285</t>
+          <t>106831</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>127448</t>
+          <t>127253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>125887</t>
+          <t>124435</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>158034</t>
+          <t>156383</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>130804</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162956</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>264926</t>
+          <t>265693</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>311705</t>
+          <t>313158</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>345325</t>
+          <t>346976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>377472</t>
+          <t>378924</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>365593</t>
+          <t>362507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>397745</t>
+          <t>395653</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>718750</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>766982</t>
+          <t>766215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27493</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33600</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>27988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44599</t>
+          <t>44985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33008</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43539</t>
+          <t>43756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42981</t>
+          <t>43052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68673</t>
+          <t>68287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84045</t>
+          <t>84184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>33549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34609</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>47424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>64816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>37874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>47831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65043</t>
+          <t>65223</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>37612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>28691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>39200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>35632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46737</t>
+          <t>46435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67625</t>
+          <t>67540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83609</t>
+          <t>83297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31191</t>
+          <t>30761</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36838</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53525</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30203</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40550</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57237</t>
+          <t>57304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45430</t>
+          <t>44523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>62418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>45669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63711</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95424</t>
+          <t>95957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120300</t>
+          <t>120623</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54803</t>
+          <t>54286</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71274</t>
+          <t>72181</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58066</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75731</t>
+          <t>76108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118180</t>
+          <t>117857</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>143056</t>
+          <t>142523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41242</t>
+          <t>40006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49580</t>
+          <t>49922</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71016</t>
+          <t>72199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79188</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94086</t>
+          <t>94763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89226</t>
+          <t>90462</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105794</t>
+          <t>105927</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174991</t>
+          <t>173808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>196427</t>
+          <t>196085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>164635</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>199619</t>
+          <t>199800</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>186550</t>
+          <t>189494</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>224109</t>
+          <t>224900</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>362249</t>
+          <t>360875</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>412672</t>
+          <t>412380</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>277346</t>
+          <t>277165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>312330</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>314672</t>
+          <t>313881</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>352231</t>
+          <t>349287</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>603074</t>
+          <t>603366</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>653497</t>
+          <t>654871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25660</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>25131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35051</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26334</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>37519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>55341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70745</t>
+          <t>70387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42157</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39233</t>
+          <t>39979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72841</t>
+          <t>72894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92269</t>
+          <t>92225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58428</t>
+          <t>58472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77856</t>
+          <t>77803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26597</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26387</t>
+          <t>26290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44086</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36105</t>
+          <t>36748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48211</t>
+          <t>48301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39580</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>51897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>81210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97902</t>
+          <t>97999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34846</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53664</t>
+          <t>54106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68442</t>
+          <t>68310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>31425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26118</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49775</t>
+          <t>49807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17533</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30310</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>28372</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>40725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>33862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51068</t>
+          <t>50763</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36504</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53918</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75247</t>
+          <t>75479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98773</t>
+          <t>99294</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65697</t>
+          <t>66002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82567</t>
+          <t>82903</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>65205</t>
+          <t>66544</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82619</t>
+          <t>83136</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>137115</t>
+          <t>136594</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>160641</t>
+          <t>160409</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32581</t>
+          <t>32440</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>31975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48698</t>
+          <t>48275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69113</t>
+          <t>68629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92540</t>
+          <t>93378</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79363</t>
+          <t>81092</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97072</t>
+          <t>97213</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90525</t>
+          <t>90948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107639</t>
+          <t>107248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>176336</t>
+          <t>175498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199763</t>
+          <t>200247</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>166203</t>
+          <t>166664</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>201377</t>
+          <t>201612</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>193596</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>231374</t>
+          <t>232148</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>369934</t>
+          <t>371768</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>423452</t>
+          <t>424218</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322846</t>
+          <t>322611</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>358020</t>
+          <t>357559</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>339659</t>
+          <t>338885</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>377437</t>
+          <t>374790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>671804</t>
+          <t>671038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>725322</t>
+          <t>723488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68283</t>
+          <t>68775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70342</t>
+          <t>70984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78374</t>
+          <t>78449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142281</t>
+          <t>142294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150882</t>
+          <t>150835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87337</t>
+          <t>91292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29996</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131019</t>
+          <t>124468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40317</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110378</t>
+          <t>110079</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106693</t>
+          <t>106206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119500</t>
+          <t>119040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124231</t>
+          <t>130782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>225254</t>
+          <t>225904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20715</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49588</t>
+          <t>50479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46448</t>
+          <t>46638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57344</t>
+          <t>57403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89731</t>
+          <t>91066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105405</t>
+          <t>105266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>17650</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53459</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63737</t>
+          <t>64035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59650</t>
+          <t>58320</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72713</t>
+          <t>72717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117650</t>
+          <t>116678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>134295</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31974</t>
+          <t>31345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71275</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>30635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39956</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43138</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77306</t>
+          <t>76970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89362</t>
+          <t>88939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33886</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>52291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70014</t>
+          <t>69508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84565</t>
+          <t>83885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114882</t>
+          <t>115439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>70245</t>
+          <t>70800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89205</t>
+          <t>88398</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>85055</t>
+          <t>85561</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>110226</t>
+          <t>110012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>163278</t>
+          <t>162721</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>193595</t>
+          <t>194275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>31578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>32510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53682</t>
+          <t>52687</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104390</t>
+          <t>104539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118412</t>
+          <t>118494</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>125885</t>
+          <t>125217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140821</t>
+          <t>141251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>234732</t>
+          <t>235727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>255732</t>
+          <t>255904</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>113404</t>
+          <t>111726</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>213673</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>111905</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>149274</t>
+          <t>151459</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>237586</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>348796</t>
+          <t>342996</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>459514</t>
+          <t>451065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>551334</t>
+          <t>553012</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>611754</t>
+          <t>609569</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>649123</t>
+          <t>650407</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1076971</t>
+          <t>1082771</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1186447</t>
+          <t>1188181</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
